--- a/docs/device-test-results.xlsx
+++ b/docs/device-test-results.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Android back button: closes an open menu (a song's, the sleep timer) or sheet first, then steps back through screens, and at the start puts the app in the background with the station still playing.</t>
+          <t>Android 14 or older: the header (the logo, Donate) sits below the status bar, never under the clock, in light and dark.</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -1712,19 +1712,54 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>First launch (delete and reinstall): the welcome appears once.</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr"/>
+          <t>Android back button: closes an open menu (a song's, the sleep timer) or sheet first, then steps back through screens, and at the start puts the app in the background with the station still playing.</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>The system</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>First launch (delete and reinstall): the welcome appears once.</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C7:H58">
+  <conditionalFormatting sqref="C7:H59">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -1739,7 +1774,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="C7:H58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C7:H59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1798,23 +1833,23 @@
         </is>
       </c>
       <c r="B2">
-        <f>COUNTIF(Results!C7:C58,"Pass")</f>
+        <f>COUNTIF(Results!C7:C59,"Pass")</f>
         <v/>
       </c>
       <c r="C2">
-        <f>COUNTIF(Results!C7:C58,"Fail")</f>
+        <f>COUNTIF(Results!C7:C59,"Fail")</f>
         <v/>
       </c>
       <c r="D2">
-        <f>COUNTIF(Results!C7:C58,"Blocked")</f>
+        <f>COUNTIF(Results!C7:C59,"Blocked")</f>
         <v/>
       </c>
       <c r="E2">
-        <f>COUNTIF(Results!C7:C58,"N/A")</f>
+        <f>COUNTIF(Results!C7:C59,"N/A")</f>
         <v/>
       </c>
       <c r="F2">
-        <f>COUNTBLANK(Results!C7:C58)</f>
+        <f>COUNTBLANK(Results!C7:C59)</f>
         <v/>
       </c>
     </row>
@@ -1825,23 +1860,23 @@
         </is>
       </c>
       <c r="B3">
-        <f>COUNTIF(Results!D7:D58,"Pass")</f>
+        <f>COUNTIF(Results!D7:D59,"Pass")</f>
         <v/>
       </c>
       <c r="C3">
-        <f>COUNTIF(Results!D7:D58,"Fail")</f>
+        <f>COUNTIF(Results!D7:D59,"Fail")</f>
         <v/>
       </c>
       <c r="D3">
-        <f>COUNTIF(Results!D7:D58,"Blocked")</f>
+        <f>COUNTIF(Results!D7:D59,"Blocked")</f>
         <v/>
       </c>
       <c r="E3">
-        <f>COUNTIF(Results!D7:D58,"N/A")</f>
+        <f>COUNTIF(Results!D7:D59,"N/A")</f>
         <v/>
       </c>
       <c r="F3">
-        <f>COUNTBLANK(Results!D7:D58)</f>
+        <f>COUNTBLANK(Results!D7:D59)</f>
         <v/>
       </c>
     </row>
@@ -1852,23 +1887,23 @@
         </is>
       </c>
       <c r="B4">
-        <f>COUNTIF(Results!E7:E58,"Pass")</f>
+        <f>COUNTIF(Results!E7:E59,"Pass")</f>
         <v/>
       </c>
       <c r="C4">
-        <f>COUNTIF(Results!E7:E58,"Fail")</f>
+        <f>COUNTIF(Results!E7:E59,"Fail")</f>
         <v/>
       </c>
       <c r="D4">
-        <f>COUNTIF(Results!E7:E58,"Blocked")</f>
+        <f>COUNTIF(Results!E7:E59,"Blocked")</f>
         <v/>
       </c>
       <c r="E4">
-        <f>COUNTIF(Results!E7:E58,"N/A")</f>
+        <f>COUNTIF(Results!E7:E59,"N/A")</f>
         <v/>
       </c>
       <c r="F4">
-        <f>COUNTBLANK(Results!E7:E58)</f>
+        <f>COUNTBLANK(Results!E7:E59)</f>
         <v/>
       </c>
     </row>
@@ -1879,23 +1914,23 @@
         </is>
       </c>
       <c r="B5">
-        <f>COUNTIF(Results!F7:F58,"Pass")</f>
+        <f>COUNTIF(Results!F7:F59,"Pass")</f>
         <v/>
       </c>
       <c r="C5">
-        <f>COUNTIF(Results!F7:F58,"Fail")</f>
+        <f>COUNTIF(Results!F7:F59,"Fail")</f>
         <v/>
       </c>
       <c r="D5">
-        <f>COUNTIF(Results!F7:F58,"Blocked")</f>
+        <f>COUNTIF(Results!F7:F59,"Blocked")</f>
         <v/>
       </c>
       <c r="E5">
-        <f>COUNTIF(Results!F7:F58,"N/A")</f>
+        <f>COUNTIF(Results!F7:F59,"N/A")</f>
         <v/>
       </c>
       <c r="F5">
-        <f>COUNTBLANK(Results!F7:F58)</f>
+        <f>COUNTBLANK(Results!F7:F59)</f>
         <v/>
       </c>
     </row>
@@ -1906,23 +1941,23 @@
         </is>
       </c>
       <c r="B6">
-        <f>COUNTIF(Results!G7:G58,"Pass")</f>
+        <f>COUNTIF(Results!G7:G59,"Pass")</f>
         <v/>
       </c>
       <c r="C6">
-        <f>COUNTIF(Results!G7:G58,"Fail")</f>
+        <f>COUNTIF(Results!G7:G59,"Fail")</f>
         <v/>
       </c>
       <c r="D6">
-        <f>COUNTIF(Results!G7:G58,"Blocked")</f>
+        <f>COUNTIF(Results!G7:G59,"Blocked")</f>
         <v/>
       </c>
       <c r="E6">
-        <f>COUNTIF(Results!G7:G58,"N/A")</f>
+        <f>COUNTIF(Results!G7:G59,"N/A")</f>
         <v/>
       </c>
       <c r="F6">
-        <f>COUNTBLANK(Results!G7:G58)</f>
+        <f>COUNTBLANK(Results!G7:G59)</f>
         <v/>
       </c>
     </row>
@@ -1933,23 +1968,23 @@
         </is>
       </c>
       <c r="B7">
-        <f>COUNTIF(Results!H7:H58,"Pass")</f>
+        <f>COUNTIF(Results!H7:H59,"Pass")</f>
         <v/>
       </c>
       <c r="C7">
-        <f>COUNTIF(Results!H7:H58,"Fail")</f>
+        <f>COUNTIF(Results!H7:H59,"Fail")</f>
         <v/>
       </c>
       <c r="D7">
-        <f>COUNTIF(Results!H7:H58,"Blocked")</f>
+        <f>COUNTIF(Results!H7:H59,"Blocked")</f>
         <v/>
       </c>
       <c r="E7">
-        <f>COUNTIF(Results!H7:H58,"N/A")</f>
+        <f>COUNTIF(Results!H7:H59,"N/A")</f>
         <v/>
       </c>
       <c r="F7">
-        <f>COUNTBLANK(Results!H7:H58)</f>
+        <f>COUNTBLANK(Results!H7:H59)</f>
         <v/>
       </c>
     </row>
